--- a/EKG_Kalite_Yönetim_Sistemi/07_Standart İş ve Uygunsuz Ürün/02_SW2 - Yeniden İşleme ve Özel Proses/EKG-URT-FRM-15_yeniden_isleme_kontrol_ve_izlenebilirlik_takip_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/07_Standart İş ve Uygunsuz Ürün/02_SW2 - Yeniden İşleme ve Özel Proses/EKG-URT-FRM-15_yeniden_isleme_kontrol_ve_izlenebilirlik_takip_formu.xlsx
@@ -953,7 +953,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-FRM-15&amp;C&amp;"Arial,Regular"&amp;11Yeniden İşleme Kontrol ve İzlenebilirlik Takip Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Yönetici paneli ve süre alanı çıkarıldı; lot/seri, işlem yetkisi, miktar, kontrol ve akıbet kaydı sadeleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>